--- a/human_resources_forms/011_curriculum_development_leave_of_absence_request--human_resources_forms.xlsx
+++ b/human_resources_forms/011_curriculum_development_leave_of_absence_request--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,110 +635,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>approved_by</t>
+          <t>leave_type</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Approved By</t>
+          <t>Leave Type</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Start Date</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>end_date</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>End Date</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>reason</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Reason</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>team_lead_approve</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Team Lead Approve</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -753,12 +684,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -849,68 +780,51 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>approved_by_choices</t>
+          <t>leave_type_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>vacation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Vacation</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>approved_by_choices</t>
+          <t>leave_type_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sick</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sick</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>team_lead_approve_choices</t>
+          <t>leave_type_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>personal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>team_lead_approve_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Personal</t>
         </is>
       </c>
     </row>
